--- a/Excel/SceneItem.xlsx
+++ b/Excel/SceneItem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76785A67-B4D5-4536-92A8-431D612E5FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD50F1BE-F15B-4E45-83F0-8E0CB868FFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,27 +125,6 @@
     <t>Meat</t>
   </si>
   <si>
-    <t>Weapon/CodyWeapon</t>
-  </si>
-  <si>
-    <t>Weapon/GuyWeapon</t>
-  </si>
-  <si>
-    <t>Weapon/HaggerWeapon</t>
-  </si>
-  <si>
-    <t>SceneItem/Tea</t>
-  </si>
-  <si>
-    <t>SceneItem/Apple</t>
-  </si>
-  <si>
-    <t>SceneItem/Cake</t>
-  </si>
-  <si>
-    <t>SceneItem/Meat</t>
-  </si>
-  <si>
     <t>type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -182,23 +161,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SceneItem/UP1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>生命或经验</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SceneItem/UP2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>UP1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UP2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon/CodyWeapon.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon/GuyWeapon.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon/HaggerWeapon.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneItem/Tea.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneItem/Apple.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneItem/Cake.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneItem/Meat.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneItem/UP1.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneItem/UP2.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -584,13 +591,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -613,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -625,16 +632,16 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -655,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -664,7 +671,7 @@
         <v>500</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -676,7 +683,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -685,7 +692,7 @@
         <v>500</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -697,7 +704,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -706,7 +713,7 @@
         <v>500</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -717,7 +724,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3">
         <v>2</v>
@@ -726,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -737,7 +744,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3">
         <v>2</v>
@@ -746,7 +753,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -757,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3">
         <v>2</v>
@@ -766,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -777,7 +784,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E11" s="3">
         <v>2</v>
@@ -786,7 +793,7 @@
         <v>34</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -794,10 +801,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="E12" s="3">
         <v>4</v>
@@ -806,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -814,10 +821,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="E13" s="3">
         <v>4</v>
@@ -826,7 +833,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SceneItem.xlsx
+++ b/Excel/SceneItem.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD50F1BE-F15B-4E45-83F0-8E0CB868FFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2406D2-3E78-45B7-84CE-62CD89D7A85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="SceneItem" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -157,10 +157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fasle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>生命或经验</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -206,6 +202,10 @@
   </si>
   <si>
     <t>SceneItem/UP2.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -270,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -283,6 +283,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,7 +641,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>22</v>
@@ -662,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -683,7 +686,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -704,7 +707,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -724,7 +727,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="3">
         <v>2</v>
@@ -732,8 +735,8 @@
       <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>24</v>
+      <c r="G8" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -744,7 +747,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3">
         <v>2</v>
@@ -752,8 +755,8 @@
       <c r="F9" s="3">
         <v>2</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>24</v>
+      <c r="G9" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -764,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3">
         <v>2</v>
@@ -772,8 +775,8 @@
       <c r="F10" s="3">
         <v>3</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>24</v>
+      <c r="G10" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -784,7 +787,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3">
         <v>2</v>
@@ -792,8 +795,8 @@
       <c r="F11" s="3">
         <v>34</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
+      <c r="G11" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -801,10 +804,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" s="3">
         <v>4</v>
@@ -812,8 +815,8 @@
       <c r="F12" s="3">
         <v>1</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>24</v>
+      <c r="G12" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -821,10 +824,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3">
         <v>4</v>
@@ -832,8 +835,8 @@
       <c r="F13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>24</v>
+      <c r="G13" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
